--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:34:55</t>
+          <t>2026-06-24 04:12:18</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:02</t>
+          <t>2026-06-24 04:12:26</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:08</t>
+          <t>2026-06-24 04:12:32</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:12</t>
+          <t>2026-06-24 04:12:37</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:17</t>
+          <t>2026-06-24 04:12:41</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:27</t>
+          <t>2026-06-24 04:12:52</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:34</t>
+          <t>2026-06-24 04:12:58</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:40</t>
+          <t>2026-06-24 04:13:03</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:34:55</t>
+          <t>2026-06-24 04:12:18</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:02</t>
+          <t>2026-06-24 04:12:26</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:08</t>
+          <t>2026-06-24 04:12:32</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:12</t>
+          <t>2026-06-24 04:12:37</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:17</t>
+          <t>2026-06-24 04:12:41</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:27</t>
+          <t>2026-06-24 04:12:52</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:34</t>
+          <t>2026-06-24 04:12:58</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:37</t>
+          <t>2026-06-24 04:13:01</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:40</t>
+          <t>2026-06-24 04:13:03</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:42</t>
+          <t>2026-06-24 04:13:05</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 02:35:43</t>
+          <t>2026-06-24 04:13:06</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:18</t>
+          <t>2026-06-24 04:35:05</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:26</t>
+          <t>2026-06-24 04:35:12</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:32</t>
+          <t>2026-06-24 04:35:17</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:37</t>
+          <t>2026-06-24 04:35:22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:41</t>
+          <t>2026-06-24 04:35:26</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:52</t>
+          <t>2026-06-24 04:35:37</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:58</t>
+          <t>2026-06-24 04:35:43</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:03</t>
+          <t>2026-06-24 04:35:49</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:18</t>
+          <t>2026-06-24 04:35:05</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:26</t>
+          <t>2026-06-24 04:35:12</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:32</t>
+          <t>2026-06-24 04:35:17</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:37</t>
+          <t>2026-06-24 04:35:22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:41</t>
+          <t>2026-06-24 04:35:26</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:52</t>
+          <t>2026-06-24 04:35:37</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:12:58</t>
+          <t>2026-06-24 04:35:43</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:01</t>
+          <t>2026-06-24 04:35:47</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22053,7 +22053,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:03</t>
+          <t>2026-06-24 04:35:49</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:05</t>
+          <t>2026-06-24 04:35:51</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 04:13:06</t>
+          <t>2026-06-24 04:35:52</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:05</t>
+          <t>2026-06-24 06:03:40</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:12</t>
+          <t>2026-06-24 06:03:46</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:17</t>
+          <t>2026-06-24 06:03:52</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:22</t>
+          <t>2026-06-24 06:03:56</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:26</t>
+          <t>2026-06-24 06:04:01</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:37</t>
+          <t>2026-06-24 06:04:10</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:43</t>
+          <t>2026-06-24 06:04:16</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:49</t>
+          <t>2026-06-24 06:04:21</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:05</t>
+          <t>2026-06-24 06:03:40</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:12</t>
+          <t>2026-06-24 06:03:46</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:17</t>
+          <t>2026-06-24 06:03:52</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:22</t>
+          <t>2026-06-24 06:03:56</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:26</t>
+          <t>2026-06-24 06:04:01</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:37</t>
+          <t>2026-06-24 06:04:10</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:43</t>
+          <t>2026-06-24 06:04:16</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:47</t>
+          <t>2026-06-24 06:04:19</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22053,7 +22053,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:49</t>
+          <t>2026-06-24 06:04:21</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:23</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:51</t>
+          <t>2026-06-24 06:04:24</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 04:35:52</t>
+          <t>2026-06-24 06:04:25</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:40</t>
+          <t>2026-06-24 06:40:03</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:46</t>
+          <t>2026-06-24 06:40:10</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:52</t>
+          <t>2026-06-24 06:40:16</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:56</t>
+          <t>2026-06-24 06:40:20</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:01</t>
+          <t>2026-06-24 06:40:25</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:10</t>
+          <t>2026-06-24 06:40:35</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:16</t>
+          <t>2026-06-24 06:40:41</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:21</t>
+          <t>2026-06-24 06:40:47</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:40</t>
+          <t>2026-06-24 06:40:03</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:46</t>
+          <t>2026-06-24 06:40:10</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:52</t>
+          <t>2026-06-24 06:40:16</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:03:56</t>
+          <t>2026-06-24 06:40:20</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:01</t>
+          <t>2026-06-24 06:40:25</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:10</t>
+          <t>2026-06-24 06:40:35</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:16</t>
+          <t>2026-06-24 06:40:41</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:19</t>
+          <t>2026-06-24 06:40:45</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:21</t>
+          <t>2026-06-24 06:40:47</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:23</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:24</t>
+          <t>2026-06-24 06:40:49</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 06:04:25</t>
+          <t>2026-06-24 06:40:50</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:03</t>
+          <t>2026-06-24 07:22:05</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:10</t>
+          <t>2026-06-24 07:22:12</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:16</t>
+          <t>2026-06-24 07:22:17</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:20</t>
+          <t>2026-06-24 07:22:22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:25</t>
+          <t>2026-06-24 07:22:26</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:35</t>
+          <t>2026-06-24 07:22:36</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:41</t>
+          <t>2026-06-24 07:22:42</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:47</t>
+          <t>2026-06-24 07:22:48</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:03</t>
+          <t>2026-06-24 07:22:05</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:10</t>
+          <t>2026-06-24 07:22:12</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:16</t>
+          <t>2026-06-24 07:22:17</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:20</t>
+          <t>2026-06-24 07:22:22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:25</t>
+          <t>2026-06-24 07:22:26</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:35</t>
+          <t>2026-06-24 07:22:36</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:41</t>
+          <t>2026-06-24 07:22:42</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:45</t>
+          <t>2026-06-24 07:22:45</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:47</t>
+          <t>2026-06-24 07:22:48</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:49</t>
+          <t>2026-06-24 07:22:50</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 06:40:50</t>
+          <t>2026-06-24 07:22:51</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:05</t>
+          <t>2026-06-24 07:50:42</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:12</t>
+          <t>2026-06-24 07:50:49</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:17</t>
+          <t>2026-06-24 07:50:53</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:22</t>
+          <t>2026-06-24 07:50:58</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:26</t>
+          <t>2026-06-24 07:51:02</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:36</t>
+          <t>2026-06-24 07:51:12</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:42</t>
+          <t>2026-06-24 07:51:17</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:48</t>
+          <t>2026-06-24 07:51:23</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:05</t>
+          <t>2026-06-24 07:50:42</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:12</t>
+          <t>2026-06-24 07:50:49</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:17</t>
+          <t>2026-06-24 07:50:53</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:22</t>
+          <t>2026-06-24 07:50:58</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:26</t>
+          <t>2026-06-24 07:51:02</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:36</t>
+          <t>2026-06-24 07:51:12</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:42</t>
+          <t>2026-06-24 07:51:17</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:45</t>
+          <t>2026-06-24 07:51:21</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:48</t>
+          <t>2026-06-24 07:51:23</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:50</t>
+          <t>2026-06-24 07:51:25</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 07:22:51</t>
+          <t>2026-06-24 07:51:26</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:42</t>
+          <t>2026-06-24 08:12:45</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:49</t>
+          <t>2026-06-24 08:12:51</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:53</t>
+          <t>2026-06-24 08:12:56</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:58</t>
+          <t>2026-06-24 08:13:01</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:02</t>
+          <t>2026-06-24 08:13:05</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:12</t>
+          <t>2026-06-24 08:13:15</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:17</t>
+          <t>2026-06-24 08:13:21</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:23</t>
+          <t>2026-06-24 08:13:26</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:42</t>
+          <t>2026-06-24 08:12:45</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:49</t>
+          <t>2026-06-24 08:12:51</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:53</t>
+          <t>2026-06-24 08:12:56</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:50:58</t>
+          <t>2026-06-24 08:13:01</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:02</t>
+          <t>2026-06-24 08:13:05</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:12</t>
+          <t>2026-06-24 08:13:15</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:17</t>
+          <t>2026-06-24 08:13:21</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:21</t>
+          <t>2026-06-24 08:13:24</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:23</t>
+          <t>2026-06-24 08:13:26</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:28</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:25</t>
+          <t>2026-06-24 08:13:29</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 07:51:26</t>
+          <t>2026-06-24 08:13:30</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:12:45</t>
+          <t>2026-06-24 09:19:59</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:12:51</t>
+          <t>2026-06-24 09:20:06</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:12:56</t>
+          <t>2026-06-24 09:20:11</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:01</t>
+          <t>2026-06-24 09:20:16</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:05</t>
+          <t>2026-06-24 09:20:21</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:15</t>
+          <t>2026-06-24 09:20:31</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:21</t>
+          <t>2026-06-24 09:20:37</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:26</t>
+          <t>2026-06-24 09:20:43</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:12:45</t>
+          <t>2026-06-24 09:19:59</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:12:51</t>
+          <t>2026-06-24 09:20:06</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:12:56</t>
+          <t>2026-06-24 09:20:11</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:01</t>
+          <t>2026-06-24 09:20:16</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:05</t>
+          <t>2026-06-24 09:20:21</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:15</t>
+          <t>2026-06-24 09:20:31</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:21</t>
+          <t>2026-06-24 09:20:37</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:24</t>
+          <t>2026-06-24 09:20:41</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:26</t>
+          <t>2026-06-24 09:20:43</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32437,7 +32437,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:28</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -32741,7 +32741,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -32893,7 +32893,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -32931,7 +32931,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -33159,7 +33159,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -33273,7 +33273,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -33577,7 +33577,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -33881,7 +33881,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34223,7 +34223,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34261,7 +34261,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34299,7 +34299,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -34565,7 +34565,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -34603,7 +34603,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -34717,7 +34717,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -34755,7 +34755,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -34831,7 +34831,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -35097,7 +35097,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35211,7 +35211,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35249,7 +35249,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -35287,7 +35287,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -35363,7 +35363,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -35401,7 +35401,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -35515,7 +35515,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -35553,7 +35553,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -35591,7 +35591,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -35629,7 +35629,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -35667,7 +35667,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -35743,7 +35743,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -35857,7 +35857,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -35971,7 +35971,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -36009,7 +36009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -36047,7 +36047,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -36123,7 +36123,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -36199,7 +36199,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -36275,7 +36275,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -36351,7 +36351,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -36427,7 +36427,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -36503,7 +36503,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -36541,7 +36541,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -36579,7 +36579,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -36655,7 +36655,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -36807,7 +36807,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:29</t>
+          <t>2026-06-24 09:20:45</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -37090,7 +37090,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:13:30</t>
+          <t>2026-06-24 09:20:46</t>
         </is>
       </c>
     </row>

--- a/reports/latest/web/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/web/Excel/Automation_Test_Report.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:19:59</t>
+          <t>2026-06-24 09:33:06</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:06</t>
+          <t>2026-06-24 09:33:13</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:11</t>
+          <t>2026-06-24 09:33:17</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:16</t>
+          <t>2026-06-24 09:33:22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:21</t>
+          <t>2026-06-24 09:33:27</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:31</t>
+          <t>2026-06-24 09:33:37</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:37</t>
+          <t>2026-06-24 09:33:43</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:43</t>
+          <t>2026-06-24 09:33:49</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18571,7 +18571,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:19:59</t>
+          <t>2026-06-24 09:33:06</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:06</t>
+          <t>2026-06-24 09:33:13</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:11</t>
+          <t>2026-06-24 09:33:17</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:16</t>
+          <t>2026-06-24 09:33:22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:21</t>
+          <t>2026-06-24 09:33:27</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:31</t>
+          <t>2026-06-24 09:33:37</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:37</t>
+          <t>2026-06-24 09:33:43</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:40</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -20543,7 +20543,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -20581,7 +20581,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:41</t>
+          <t>2026-06-24 09:33:47</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:43</t>
+          <t>2026-06-24 09:33:49</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -24229,7 +24229,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -24305,7 +24305,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -24343,7 +24343,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -25293,7 +25293,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -26927,7 +26927,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -27117,7 +27117,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -27497,7 +27497,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -27877,7 +27877,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -28067,7 +28067,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -28295,7 +28295,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -28447,7 +28447,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -29055,7 +29055,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29283,7 +29283,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29359,7 +29359,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -29625,7 +29625,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -29967,7 +29967,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -30005,7 +30005,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -30081,7 +30081,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30879,7 +30879,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -31031,7 +31031,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -31411,7 +31411,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -31525,7 +31525,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -31715,7 +31715,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -31905,7 +31905,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -31943,7 +31943,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:20:45</t>
+          <t>2026-06-24 09:33:51</t>
         </is>
       </c>
     